--- a/files/WMSOK.xlsx
+++ b/files/WMSOK.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t>codigo</t>
   </si>
@@ -546,6 +546,12 @@
   </si>
   <si>
     <t>VD2T</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
   </si>
   <si>
     <t>cantidad</t>
@@ -2877,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2924,145 +2930,145 @@
   <sheetData>
     <row r="1" ht="51" customHeight="1">
       <c r="A1" s="53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H1" s="54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I1" s="54" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J1" s="54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K1" s="54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L1" s="54" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="O1" s="56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P1" s="56" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q1" s="56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="R1" s="56" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="S1" s="56" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T1" s="56" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="U1" s="57" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="V1" s="57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="W1" s="57" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="X1" s="57" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Y1" s="57" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z1" s="58" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA1" s="58" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AB1" s="58" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AC1" s="58" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AD1" s="58" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AE1" s="58" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AF1" s="58" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG1" s="59" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AH1" s="59" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AI1" s="59" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ1" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="AK1" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="AL1" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="AM1" s="60" t="s">
         <v>271</v>
       </c>
-      <c r="AJ1" s="59" t="s">
+      <c r="AN1" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="AK1" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL1" s="59" t="s">
+      <c r="AO1" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="AM1" s="60" t="s">
-        <v>269</v>
-      </c>
-      <c r="AN1" s="60" t="s">
-        <v>270</v>
-      </c>
-      <c r="AO1" s="60" t="s">
-        <v>271</v>
-      </c>
       <c r="AP1" s="60" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AQ1" s="60" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AR1" s="60" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AS1" s="61" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AT1" s="61" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AU1" s="61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
@@ -3109,10 +3115,10 @@
       <c r="AI2" s="63"/>
       <c r="AJ2" s="63"/>
       <c r="AK2" s="27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL2" s="27" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM2" s="63"/>
       <c r="AN2" s="63"/>
@@ -3166,10 +3172,10 @@
       <c r="AI3" s="63"/>
       <c r="AJ3" s="63"/>
       <c r="AK3" s="27" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL3" s="27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AM3" s="63"/>
       <c r="AN3" s="63"/>
@@ -3225,10 +3231,10 @@
       <c r="AI4" s="63"/>
       <c r="AJ4" s="63"/>
       <c r="AK4" s="27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL4" s="27" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM4" s="63"/>
       <c r="AN4" s="63"/>
@@ -4333,21 +4339,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -4355,10 +4361,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -4366,10 +4372,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -4377,10 +4383,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -4407,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -4417,12 +4423,12 @@
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4449,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
@@ -4463,29 +4469,29 @@
         <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B3" s="27">
         <v>350</v>
       </c>
       <c r="C3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B4" s="27">
         <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -4553,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
@@ -4605,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
@@ -4654,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="79" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
@@ -4670,7 +4676,7 @@
     </row>
     <row r="3">
       <c r="A3" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C3" s="27">
         <v>54781769398</v>
@@ -4678,7 +4684,7 @@
     </row>
     <row r="4">
       <c r="A4" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C4" s="27">
         <v>54781769406</v>
@@ -4705,7 +4711,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2">
@@ -4715,7 +4721,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -4725,7 +4731,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6">
@@ -4735,7 +4741,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
@@ -4764,12 +4770,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -6937,15 +6943,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -6956,7 +6962,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -6967,7 +6973,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -6978,7 +6984,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -7008,15 +7014,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="80" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B2">
         <v>1450</v>
@@ -7046,12 +7052,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="81" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -7078,12 +7084,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="81" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -7116,10 +7122,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
@@ -8083,10 +8092,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
@@ -8100,23 +8109,23 @@
         <v>150</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M2" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
@@ -8502,15 +8511,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2">
         <v>4200</v>
@@ -8521,7 +8530,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B3">
         <v>900</v>
@@ -8532,7 +8541,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B4">
         <v>900</v>
@@ -8566,26 +8575,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38"/>
       <c r="D1" s="37" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="39">
         <v>4200</v>
@@ -8598,7 +8607,7 @@
         <v>10710</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -8610,7 +8619,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="39">
         <v>900</v>
@@ -8623,7 +8632,7 @@
         <v>2295</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -8635,7 +8644,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B4" s="39">
         <v>900</v>
@@ -8648,7 +8657,7 @@
         <v>2295</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -8660,14 +8669,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="34">
         <v>2300</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -8679,14 +8688,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34">
         <v>132000</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -8746,26 +8755,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B3" s="43">
         <v>1200</v>
@@ -8776,7 +8785,7 @@
     </row>
     <row r="4">
       <c r="A4" s="31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B4" s="43">
         <v>1200</v>
@@ -8787,7 +8796,7 @@
     </row>
     <row r="5">
       <c r="A5" s="31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B5" s="43">
         <v>1200</v>
@@ -8798,7 +8807,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
@@ -8827,7 +8836,7 @@
     </row>
     <row r="23">
       <c r="A23" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B23" s="27">
         <v>500</v>
@@ -8835,7 +8844,7 @@
     </row>
     <row r="24">
       <c r="A24" s="31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B24" s="27">
         <v>500</v>
@@ -8843,7 +8852,7 @@
     </row>
     <row r="25">
       <c r="A25" s="31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" s="27">
         <v>500</v>
@@ -8851,19 +8860,19 @@
     </row>
     <row r="28">
       <c r="A28" s="44" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29">
@@ -8916,7 +8925,7 @@
     </row>
     <row r="32">
       <c r="A32" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B32" s="27">
         <v>100</v>
@@ -8932,7 +8941,7 @@
     </row>
     <row r="33">
       <c r="A33" s="31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B33" s="27">
         <v>100</v>
@@ -8948,7 +8957,7 @@
     </row>
     <row r="34">
       <c r="A34" s="31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B34" s="27">
         <v>400</v>
@@ -8987,10 +8996,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
@@ -9001,7 +9010,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D2" s="45">
         <v>7503041710073</v>
@@ -9015,7 +9024,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2">
         <v>7503041710097</v>
@@ -9061,135 +9070,135 @@
   <sheetData>
     <row r="1" s="48" customFormat="1">
       <c r="A1" s="48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B1" s="48" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C1" s="48" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D1" s="48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F1" s="48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G1" s="48" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H1" s="48" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I1" s="47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J1" s="48" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K1" s="46" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L1" s="48" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="R1" s="48" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="S1" s="48" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="T1" s="48" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="U1" s="48" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="V1" s="48" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="W1" s="48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E2" s="49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K2" s="46">
         <v>1800</v>
       </c>
       <c r="L2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M2">
         <v>1149</v>
       </c>
       <c r="N2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="R2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="S2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="U2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="V2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="W2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
